--- a/PROTOTYPE MONTHLY/FLOOR.xlsx
+++ b/PROTOTYPE MONTHLY/FLOOR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500" firstSheet="2" activeTab="5"/>
+    <workbookView windowWidth="15980" windowHeight="17020" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Anugrah (Bag, Cup, Box)" sheetId="1" r:id="rId1"/>
@@ -108,16 +108,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="10">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="180" formatCode="dd\-mmm"/>
-    <numFmt numFmtId="181" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="182" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="183" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??.00_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="[$-409]d\-mmm\-yyyy;@"/>
+    <numFmt numFmtId="182" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="183" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="184" formatCode="[$Rp-421]#,##0.0000;[Red][$Rp-421]#,##0.0000"/>
+    <numFmt numFmtId="185" formatCode="[$Rp-421]#,##0.00;[Red][$Rp-421]#,##0.00"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -631,19 +631,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -670,6 +657,19 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -846,16 +846,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -988,7 +988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1009,30 +1009,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1041,49 +1041,49 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1098,7 +1098,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1107,27 +1107,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1137,70 +1137,42 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1213,8 +1185,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1223,7 +1194,41 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="8" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1232,6 +1237,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1245,7 +1251,7 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1254,82 +1260,76 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1338,16 +1338,22 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1670,183 +1676,183 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.4285714285714" style="89"/>
-    <col min="2" max="2" width="13.4285714285714" style="89" customWidth="1"/>
-    <col min="3" max="3" width="36" style="89" customWidth="1"/>
-    <col min="4" max="4" width="21.2857142857143" style="88" customWidth="1"/>
-    <col min="5" max="5" width="33.2857142857143" style="89" customWidth="1"/>
-    <col min="6" max="6" width="17.2857142857143" style="89" customWidth="1"/>
-    <col min="7" max="8" width="20.8571428571429" style="89" customWidth="1"/>
-    <col min="9" max="9" width="12.8571428571429" style="89"/>
-    <col min="10" max="10" width="12" style="89"/>
-    <col min="11" max="16384" width="18.0380952380952" style="89"/>
+    <col min="1" max="1" width="17.4296875" style="93"/>
+    <col min="2" max="2" width="13.4296875" style="93" customWidth="1"/>
+    <col min="3" max="3" width="36" style="93" customWidth="1"/>
+    <col min="4" max="4" width="21.2890625" style="92" customWidth="1"/>
+    <col min="5" max="5" width="33.2890625" style="93" customWidth="1"/>
+    <col min="6" max="6" width="17.2890625" style="93" customWidth="1"/>
+    <col min="7" max="8" width="20.859375" style="93" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="93"/>
+    <col min="10" max="10" width="12" style="93"/>
+    <col min="11" max="16384" width="18.0390625" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="87" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="114" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="115" t="s">
+    <row r="1" s="91" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="115" t="s">
+      <c r="C1" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="115" t="s">
+      <c r="D1" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="115" t="s">
+      <c r="E1" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="115" t="s">
+      <c r="F1" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="115" t="s">
+      <c r="G1" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="115" t="s">
+      <c r="H1" s="119" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="87" customFormat="1" ht="60" customHeight="1" spans="1:8">
+    <row r="2" s="91" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A2" s="100"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="99">
+      <c r="B2" s="97"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="111">
         <f t="shared" ref="G2:G10" si="0">SUM(D2*F2)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="99">
+      <c r="H2" s="111">
         <f>SUM(G2:G5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="87" customFormat="1" ht="60" customHeight="1" spans="1:8">
+    <row r="3" s="91" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A3" s="102"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="116"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="99">
+      <c r="B3" s="97"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H3" s="106"/>
-    </row>
-    <row r="4" s="87" customFormat="1" ht="60" customHeight="1" spans="1:8">
+      <c r="H3" s="113"/>
+    </row>
+    <row r="4" s="91" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A4" s="102"/>
-      <c r="B4" s="93"/>
-      <c r="C4" s="116"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="99">
+      <c r="B4" s="97"/>
+      <c r="C4" s="120"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="109"/>
+      <c r="G4" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="106"/>
-    </row>
-    <row r="5" s="87" customFormat="1" ht="60" customHeight="1" spans="1:8">
+      <c r="H4" s="113"/>
+    </row>
+    <row r="5" s="91" customFormat="1" ht="60" customHeight="1" spans="1:8">
       <c r="A5" s="102"/>
-      <c r="B5" s="93"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="99">
+      <c r="B5" s="97"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5" s="106"/>
-    </row>
-    <row r="6" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="H5" s="113"/>
+    </row>
+    <row r="6" s="91" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
       <c r="A6" s="100"/>
       <c r="B6" s="101"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="99">
+      <c r="C6" s="99"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="99">
+      <c r="H6" s="111">
         <f>SUM(G6:G9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+    <row r="7" s="91" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
       <c r="A7" s="102"/>
       <c r="B7" s="103"/>
-      <c r="C7" s="93"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="99">
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="126"/>
+      <c r="G7" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="106"/>
-    </row>
-    <row r="8" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="H7" s="113"/>
+    </row>
+    <row r="8" s="91" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
       <c r="A8" s="102"/>
       <c r="B8" s="103"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="99">
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="106"/>
-    </row>
-    <row r="9" s="87" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="H8" s="113"/>
+    </row>
+    <row r="9" s="91" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
       <c r="A9" s="102"/>
       <c r="B9" s="103"/>
       <c r="C9" s="101"/>
       <c r="D9" s="101"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="99">
+      <c r="E9" s="112"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="106"/>
-    </row>
-    <row r="10" s="87" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A10" s="92"/>
-      <c r="B10" s="93"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="93"/>
-      <c r="E10" s="111"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="96">
+      <c r="H9" s="113"/>
+    </row>
+    <row r="10" s="91" customFormat="1" ht="258" customHeight="1" spans="1:8">
+      <c r="A10" s="96"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="97"/>
+      <c r="D10" s="97"/>
+      <c r="E10" s="116"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="109">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="96">
+      <c r="H10" s="109">
         <f>SUM(G10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="87" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A11" s="120" t="s">
+    <row r="11" s="91" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="A11" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="121"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="124"/>
-      <c r="F11" s="124"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="126">
+      <c r="B11" s="123"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="128"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="130">
         <f>SUM(H2:H10)</f>
         <v>0</v>
       </c>
@@ -1872,138 +1878,138 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="18.75" outlineLevelRow="7" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.8571428571429" style="88"/>
-    <col min="2" max="2" width="18.8571428571429" style="88" customWidth="1"/>
-    <col min="3" max="3" width="43.0380952380952" style="88" customWidth="1"/>
-    <col min="4" max="4" width="14.4285714285714" style="88" customWidth="1"/>
-    <col min="5" max="5" width="58.9619047619048" style="89" customWidth="1"/>
-    <col min="6" max="6" width="19.5238095238095" style="89" customWidth="1"/>
-    <col min="7" max="8" width="20.8571428571429" style="89" customWidth="1"/>
-    <col min="9" max="9" width="12.8571428571429" style="89"/>
-    <col min="10" max="16384" width="9.14285714285714" style="89"/>
+    <col min="1" max="1" width="19.859375" style="92"/>
+    <col min="2" max="2" width="18.859375" style="92" customWidth="1"/>
+    <col min="3" max="3" width="43.0390625" style="92" customWidth="1"/>
+    <col min="4" max="4" width="14.4296875" style="92" customWidth="1"/>
+    <col min="5" max="5" width="58.9609375" style="93" customWidth="1"/>
+    <col min="6" max="6" width="19.5234375" style="93" customWidth="1"/>
+    <col min="7" max="8" width="20.859375" style="93" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="93"/>
+    <col min="10" max="16384" width="9.140625" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="87" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="90" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="91" t="s">
+    <row r="1" s="91" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="94" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="91" t="s">
+      <c r="C1" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="91" t="s">
+      <c r="D1" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="91" t="s">
+      <c r="E1" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="91" t="s">
+      <c r="F1" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="G1" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="91" t="s">
+      <c r="H1" s="95" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="87" customFormat="1" ht="249.35" customHeight="1" spans="1:8">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="97">
+    <row r="2" s="91" customFormat="1" ht="249.35" customHeight="1" spans="1:8">
+      <c r="A2" s="96"/>
+      <c r="B2" s="97"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="110">
         <f>D2*F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="96">
+      <c r="H2" s="109">
         <f>SUM(G2:G2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="87" customFormat="1" ht="251.35" customHeight="1" spans="1:8">
-      <c r="A3" s="92"/>
-      <c r="B3" s="93"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="97">
+    <row r="3" s="91" customFormat="1" ht="251.35" customHeight="1" spans="1:8">
+      <c r="A3" s="96"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110">
         <f>D3*F3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="99">
+      <c r="H3" s="111">
         <f>SUM(G3:G3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
+    <row r="4" s="91" customFormat="1" ht="83" customHeight="1" spans="1:8">
       <c r="A4" s="100"/>
       <c r="B4" s="101"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="95"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97">
+      <c r="C4" s="99"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110">
         <f>D4*F4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="99">
+      <c r="H4" s="111">
         <f>SUM(G4:G6)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
+    <row r="5" s="91" customFormat="1" ht="83" customHeight="1" spans="1:8">
       <c r="A5" s="102"/>
       <c r="B5" s="103"/>
-      <c r="C5" s="98"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="104"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="99"/>
-      <c r="G5" s="97">
+      <c r="E5" s="112"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="110">
         <f>D5*F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="106"/>
-    </row>
-    <row r="6" s="87" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A6" s="107"/>
-      <c r="B6" s="108"/>
-      <c r="C6" s="98"/>
+      <c r="H5" s="113"/>
+    </row>
+    <row r="6" s="91" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A6" s="105"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="99"/>
       <c r="D6" s="104"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="97">
+      <c r="E6" s="114"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="110">
         <f>D6*F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="110"/>
-    </row>
-    <row r="7" s="87" customFormat="1" ht="200" customHeight="1" spans="1:8">
-      <c r="A7" s="92"/>
-      <c r="B7" s="93"/>
-      <c r="C7" s="98"/>
+      <c r="H6" s="115"/>
+    </row>
+    <row r="7" s="91" customFormat="1" ht="200" customHeight="1" spans="1:8">
+      <c r="A7" s="96"/>
+      <c r="B7" s="97"/>
+      <c r="C7" s="99"/>
       <c r="D7" s="104"/>
-      <c r="E7" s="111"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="96"/>
-    </row>
-    <row r="8" s="87" customFormat="1" spans="1:8">
-      <c r="A8" s="112"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="113">
+      <c r="E7" s="116"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="109"/>
+    </row>
+    <row r="8" s="91" customFormat="1" spans="1:8">
+      <c r="A8" s="107"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117">
         <f>SUM(H2:H7)</f>
         <v>0</v>
       </c>
@@ -2024,16 +2030,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="6"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="11.7142857142857" customWidth="1"/>
-    <col min="2" max="2" width="22.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="22.5714285714286" customWidth="1"/>
-    <col min="4" max="4" width="17.5714285714286" customWidth="1"/>
-    <col min="5" max="5" width="34.5714285714286" customWidth="1"/>
-    <col min="6" max="6" width="19.4285714285714" customWidth="1"/>
-    <col min="7" max="7" width="17.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" customWidth="1"/>
+    <col min="5" max="5" width="34.5703125" customWidth="1"/>
+    <col min="6" max="6" width="19.4296875" customWidth="1"/>
+    <col min="7" max="7" width="17.2890625" customWidth="1"/>
+    <col min="9" max="9" width="13.0625"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:7">
@@ -2064,158 +2071,170 @@
       <c r="B2" s="39"/>
       <c r="C2" s="53"/>
       <c r="D2" s="54"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="57">
+      <c r="E2" s="73"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="75">
         <f>SUM(D2*F2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="123.5" customHeight="1" spans="1:7">
+    <row r="3" ht="191" customHeight="1" spans="1:7">
       <c r="A3" s="52"/>
       <c r="B3" s="39"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="57"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="75"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="52"/>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62">
+      <c r="C4" s="57"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="78">
         <f>SUM(G2:G3)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="I4" s="90"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="52"/>
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="61"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62">
+      <c r="C5" s="57"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="78">
         <f>G4*11%</f>
         <v>0</v>
       </c>
+      <c r="I5" s="90"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="52"/>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="63">
-        <v>243</v>
+      <c r="C6" s="57"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="78">
+        <f>((G4*100)/111)*0.111%</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="52"/>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="81">
+        <f>SUM(G4:G6)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="123.5" customHeight="1" spans="1:7">
       <c r="A8" s="52"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="66"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="69"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="75"/>
     </row>
     <row r="9" ht="123.5" customHeight="1" spans="1:7">
       <c r="A9" s="52"/>
-      <c r="B9" s="70"/>
-      <c r="C9" s="66"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="69"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="75"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="72"/>
-      <c r="B10" s="61" t="s">
+      <c r="A10" s="63"/>
+      <c r="B10" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62">
+      <c r="C10" s="57"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="78">
         <f>SUM(G8:G9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="74"/>
-      <c r="B11" s="75" t="s">
+      <c r="A11" s="64"/>
+      <c r="B11" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="78">
+        <f>G10*11%</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="72"/>
-      <c r="B12" s="61" t="s">
+      <c r="A12" s="63"/>
+      <c r="B12" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="63"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="78">
+        <f>((G10*100)/111)*0.111%</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="77"/>
-      <c r="B13" s="78" t="s">
+      <c r="A13" s="67"/>
+      <c r="B13" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="80"/>
-      <c r="G13" s="64">
+      <c r="C13" s="69"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="81">
         <f>SUM(G10:G12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="82"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="84">
+      <c r="B14" s="71"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="87">
         <f>G7+G13</f>
         <v>0</v>
       </c>
-      <c r="F14" s="85"/>
-      <c r="G14" s="86"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="89"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
@@ -2236,6 +2255,7 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G8:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2246,14 +2266,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="10.5714285714286" style="12" customWidth="1"/>
-    <col min="2" max="2" width="12.6" style="36" customWidth="1"/>
-    <col min="3" max="3" width="36.1238095238095" style="12" customWidth="1"/>
-    <col min="4" max="4" width="18.8285714285714" style="12" customWidth="1"/>
-    <col min="5" max="5" width="12.2857142857143" style="12" customWidth="1"/>
-    <col min="6" max="16384" width="9.14285714285714" style="12"/>
+    <col min="1" max="1" width="10.5703125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="12.6015625" style="36" customWidth="1"/>
+    <col min="3" max="3" width="36.125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="18.828125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="12.2890625" style="12" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" s="35" customFormat="1" ht="19" customHeight="1" spans="1:5">
@@ -2285,147 +2305,147 @@
       <c r="B3" s="40"/>
       <c r="C3" s="41"/>
       <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
+      <c r="E3" s="48"/>
     </row>
     <row r="4" s="12" customFormat="1" ht="249.95" customHeight="1" spans="1:5">
       <c r="A4" s="39"/>
       <c r="B4" s="40"/>
       <c r="C4" s="41"/>
       <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
+      <c r="E4" s="48"/>
     </row>
     <row r="5" s="12" customFormat="1" ht="256.25" customHeight="1" spans="1:5">
       <c r="A5" s="39"/>
       <c r="B5" s="40"/>
       <c r="C5" s="41"/>
       <c r="D5" s="43"/>
-      <c r="E5" s="44"/>
+      <c r="E5" s="48"/>
     </row>
     <row r="6" s="12" customFormat="1" ht="253.85" customHeight="1" spans="1:5">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="41"/>
       <c r="D6" s="43"/>
-      <c r="E6" s="44"/>
+      <c r="E6" s="48"/>
     </row>
     <row r="7" s="12" customFormat="1" ht="254.65" customHeight="1" spans="1:5">
       <c r="A7" s="39"/>
       <c r="B7" s="40"/>
       <c r="C7" s="41"/>
       <c r="D7" s="43"/>
-      <c r="E7" s="44"/>
+      <c r="E7" s="48"/>
     </row>
     <row r="8" s="12" customFormat="1" ht="255.35" customHeight="1" spans="1:5">
       <c r="A8" s="39"/>
       <c r="B8" s="40"/>
       <c r="C8" s="41"/>
       <c r="D8" s="43"/>
-      <c r="E8" s="44"/>
+      <c r="E8" s="48"/>
     </row>
     <row r="9" s="12" customFormat="1" ht="266.95" customHeight="1" spans="1:5">
       <c r="A9" s="39"/>
       <c r="B9" s="40"/>
       <c r="C9" s="41"/>
       <c r="D9" s="43"/>
-      <c r="E9" s="44"/>
+      <c r="E9" s="48"/>
     </row>
     <row r="10" s="12" customFormat="1" ht="261.95" customHeight="1" spans="1:5">
       <c r="A10" s="39"/>
       <c r="B10" s="40"/>
       <c r="C10" s="41"/>
       <c r="D10" s="43"/>
-      <c r="E10" s="44"/>
+      <c r="E10" s="48"/>
     </row>
     <row r="11" s="12" customFormat="1" ht="261.9" customHeight="1" spans="1:5">
       <c r="A11" s="39"/>
       <c r="B11" s="40"/>
       <c r="C11" s="41"/>
       <c r="D11" s="43"/>
-      <c r="E11" s="44"/>
+      <c r="E11" s="48"/>
     </row>
     <row r="12" s="12" customFormat="1" ht="270.7" customHeight="1" spans="1:5">
       <c r="A12" s="39"/>
       <c r="B12" s="40"/>
       <c r="C12" s="41"/>
       <c r="D12" s="43"/>
-      <c r="E12" s="44"/>
+      <c r="E12" s="48"/>
     </row>
     <row r="13" s="12" customFormat="1" ht="261.1" customHeight="1" spans="1:5">
       <c r="A13" s="39"/>
       <c r="B13" s="40"/>
       <c r="C13" s="41"/>
       <c r="D13" s="43"/>
-      <c r="E13" s="44"/>
+      <c r="E13" s="48"/>
     </row>
     <row r="14" s="12" customFormat="1" ht="257.15" customHeight="1" spans="1:5">
       <c r="A14" s="39"/>
       <c r="B14" s="40"/>
       <c r="C14" s="41"/>
       <c r="D14" s="43"/>
-      <c r="E14" s="44"/>
+      <c r="E14" s="48"/>
     </row>
     <row r="15" s="12" customFormat="1" ht="263.55" customHeight="1" spans="1:5">
       <c r="A15" s="39"/>
       <c r="B15" s="40"/>
       <c r="C15" s="41"/>
       <c r="D15" s="43"/>
-      <c r="E15" s="44"/>
+      <c r="E15" s="48"/>
     </row>
     <row r="16" s="12" customFormat="1" ht="270.35" customHeight="1" spans="1:5">
       <c r="A16" s="39"/>
       <c r="B16" s="40"/>
       <c r="C16" s="41"/>
       <c r="D16" s="43"/>
-      <c r="E16" s="44"/>
+      <c r="E16" s="48"/>
     </row>
     <row r="17" s="12" customFormat="1" ht="261.7" customHeight="1" spans="1:5">
       <c r="A17" s="39"/>
       <c r="B17" s="40"/>
       <c r="C17" s="41"/>
       <c r="D17" s="43"/>
-      <c r="E17" s="44"/>
+      <c r="E17" s="48"/>
     </row>
     <row r="18" s="12" customFormat="1" ht="260" customHeight="1" spans="1:5">
       <c r="A18" s="39"/>
       <c r="B18" s="40"/>
       <c r="C18" s="41"/>
       <c r="D18" s="43"/>
-      <c r="E18" s="44"/>
+      <c r="E18" s="48"/>
     </row>
     <row r="19" s="12" customFormat="1" ht="263.2" customHeight="1" spans="1:5">
       <c r="A19" s="39"/>
       <c r="B19" s="40"/>
       <c r="C19" s="41"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="44"/>
+      <c r="E19" s="48"/>
     </row>
     <row r="20" s="12" customFormat="1" ht="289.95" customHeight="1" spans="1:5">
       <c r="A20" s="39"/>
       <c r="B20" s="40"/>
       <c r="C20" s="41"/>
       <c r="D20" s="43"/>
-      <c r="E20" s="44"/>
+      <c r="E20" s="48"/>
     </row>
     <row r="21" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
       <c r="A21" s="39"/>
       <c r="B21" s="40"/>
       <c r="C21" s="41"/>
       <c r="D21" s="43"/>
-      <c r="E21" s="44"/>
+      <c r="E21" s="48"/>
     </row>
     <row r="22" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
       <c r="A22" s="39"/>
       <c r="B22" s="40"/>
       <c r="C22" s="41"/>
       <c r="D22" s="43"/>
-      <c r="E22" s="44"/>
+      <c r="E22" s="48"/>
     </row>
     <row r="23" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
       <c r="A23" s="39"/>
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
       <c r="D23" s="43"/>
-      <c r="E23" s="44"/>
+      <c r="E23" s="48"/>
     </row>
     <row r="24" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
       <c r="A24" s="39"/>
@@ -2488,13 +2508,13 @@
       <c r="E31" s="41"/>
     </row>
     <row r="32" s="12" customFormat="1" spans="1:5">
-      <c r="A32" s="45"/>
-      <c r="B32" s="46"/>
-      <c r="C32" s="47">
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="46">
         <f>SUM(D2:D31)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="48"/>
+      <c r="D32" s="47"/>
       <c r="E32" s="49"/>
     </row>
   </sheetData>
@@ -2511,14 +2531,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="21.1428571428571" style="13" customWidth="1"/>
-    <col min="2" max="2" width="27.5714285714286" style="12" customWidth="1"/>
-    <col min="3" max="3" width="30.752380952381" style="12" customWidth="1"/>
-    <col min="4" max="4" width="65.7047619047619" style="12" customWidth="1"/>
-    <col min="5" max="7" width="32.3333333333333" style="12" customWidth="1"/>
-    <col min="8" max="16384" width="9.14285714285714" style="12"/>
+    <col min="1" max="1" width="21.140625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="27.5703125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="30.75" style="12" customWidth="1"/>
+    <col min="4" max="4" width="65.703125" style="12" customWidth="1"/>
+    <col min="5" max="7" width="32.3359375" style="12" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" s="11" customFormat="1" ht="35" customHeight="1" spans="1:7">
@@ -2549,61 +2569,61 @@
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
       <c r="D2" s="19"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21">
+      <c r="E2" s="25"/>
+      <c r="F2" s="26">
         <f>C2*E2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="27">
         <f>SUM(F2:F2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="30"/>
     </row>
     <row r="4" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A4" s="23"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="30"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="31"/>
     </row>
     <row r="5" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A5" s="23"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="31"/>
-    </row>
-    <row r="6" s="12" customFormat="1" ht="23.25" spans="1:7">
-      <c r="A6" s="23"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="32"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="32"/>
+    </row>
+    <row r="6" s="12" customFormat="1" ht="26" spans="1:7">
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="33"/>
     </row>
     <row r="7" s="12" customFormat="1" ht="39" customHeight="1" spans="1:7">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="28"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="29"/>
       <c r="G7" s="34">
         <f>SUM(G2:G6)</f>
         <v>0</v>
@@ -2624,10 +2644,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="9.14285714285714" style="1"/>
-    <col min="2" max="2" width="21.8571428571429" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="21.859375" style="2" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
   </cols>
   <sheetData>

--- a/PROTOTYPE MONTHLY/FLOOR.xlsx
+++ b/PROTOTYPE MONTHLY/FLOOR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15980" windowHeight="17020" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="16020" windowHeight="17020" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Anugrah (Bag, Cup, Box)" sheetId="1" r:id="rId1"/>
@@ -988,7 +988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1131,6 +1131,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1194,6 +1195,9 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1201,7 +1205,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="184" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1209,12 +1213,9 @@
     <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1234,9 +1235,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1678,181 +1677,181 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.4296875" style="93"/>
-    <col min="2" max="2" width="13.4296875" style="93" customWidth="1"/>
-    <col min="3" max="3" width="36" style="93" customWidth="1"/>
-    <col min="4" max="4" width="21.2890625" style="92" customWidth="1"/>
-    <col min="5" max="5" width="33.2890625" style="93" customWidth="1"/>
-    <col min="6" max="6" width="17.2890625" style="93" customWidth="1"/>
-    <col min="7" max="8" width="20.859375" style="93" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="93"/>
-    <col min="10" max="10" width="12" style="93"/>
-    <col min="11" max="16384" width="18.0390625" style="93"/>
+    <col min="1" max="1" width="17.4296875" style="94"/>
+    <col min="2" max="2" width="13.4296875" style="94" customWidth="1"/>
+    <col min="3" max="3" width="36" style="94" customWidth="1"/>
+    <col min="4" max="4" width="21.2890625" style="93" customWidth="1"/>
+    <col min="5" max="5" width="33.2890625" style="94" customWidth="1"/>
+    <col min="6" max="6" width="17.2890625" style="94" customWidth="1"/>
+    <col min="7" max="8" width="20.859375" style="94" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="94"/>
+    <col min="10" max="10" width="12" style="94"/>
+    <col min="11" max="16384" width="18.0390625" style="94"/>
   </cols>
   <sheetData>
-    <row r="1" s="91" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="119" t="s">
+    <row r="1" s="92" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="119" t="s">
+      <c r="C1" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="119" t="s">
+      <c r="D1" s="120" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="119" t="s">
+      <c r="E1" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="119" t="s">
+      <c r="F1" s="120" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="119" t="s">
+      <c r="G1" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="119" t="s">
+      <c r="H1" s="120" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="91" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A2" s="100"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="120"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="111">
+    <row r="2" s="92" customFormat="1" ht="60" customHeight="1" spans="1:8">
+      <c r="A2" s="101"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="122"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="112">
         <f t="shared" ref="G2:G10" si="0">SUM(D2*F2)</f>
         <v>0</v>
       </c>
-      <c r="H2" s="111">
+      <c r="H2" s="112">
         <f>SUM(G2:G5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="91" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A3" s="102"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="120"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="111">
+    <row r="3" s="92" customFormat="1" ht="60" customHeight="1" spans="1:8">
+      <c r="A3" s="103"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H3" s="113"/>
-    </row>
-    <row r="4" s="91" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A4" s="102"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="120"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="112"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="111">
+      <c r="H3" s="114"/>
+    </row>
+    <row r="4" s="92" customFormat="1" ht="60" customHeight="1" spans="1:8">
+      <c r="A4" s="103"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H4" s="113"/>
-    </row>
-    <row r="5" s="91" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A5" s="102"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="120"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="111">
+      <c r="H4" s="114"/>
+    </row>
+    <row r="5" s="92" customFormat="1" ht="60" customHeight="1" spans="1:8">
+      <c r="A5" s="103"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H5" s="113"/>
-    </row>
-    <row r="6" s="91" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A6" s="100"/>
-      <c r="B6" s="101"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111">
+      <c r="H5" s="114"/>
+    </row>
+    <row r="6" s="92" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A6" s="101"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="111">
+      <c r="H6" s="112">
         <f>SUM(G6:G9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="91" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A7" s="102"/>
-      <c r="B7" s="103"/>
-      <c r="C7" s="97"/>
-      <c r="D7" s="97"/>
-      <c r="E7" s="112"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="111">
+    <row r="7" s="92" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A7" s="103"/>
+      <c r="B7" s="104"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="127"/>
+      <c r="G7" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="113"/>
-    </row>
-    <row r="8" s="91" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A8" s="102"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="111">
+      <c r="H7" s="114"/>
+    </row>
+    <row r="8" s="92" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A8" s="103"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="113"/>
-    </row>
-    <row r="9" s="91" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A9" s="102"/>
-      <c r="B9" s="103"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="111">
+      <c r="H8" s="114"/>
+    </row>
+    <row r="9" s="92" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
+      <c r="A9" s="103"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="113"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="113"/>
-    </row>
-    <row r="10" s="91" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A10" s="96"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="116"/>
-      <c r="F10" s="127"/>
-      <c r="G10" s="109">
+      <c r="H9" s="114"/>
+    </row>
+    <row r="10" s="92" customFormat="1" ht="258" customHeight="1" spans="1:8">
+      <c r="A10" s="97"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="110">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="109">
+      <c r="H10" s="110">
         <f>SUM(G10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="91" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A11" s="122" t="s">
+    <row r="11" s="92" customFormat="1" ht="18" customHeight="1" spans="1:8">
+      <c r="A11" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="123"/>
-      <c r="C11" s="124"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="128"/>
-      <c r="F11" s="128"/>
-      <c r="G11" s="129"/>
-      <c r="H11" s="130">
+      <c r="B11" s="124"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="126"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="129"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="131">
         <f>SUM(H2:H10)</f>
         <v>0</v>
       </c>
@@ -1880,136 +1879,136 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.859375" style="92"/>
-    <col min="2" max="2" width="18.859375" style="92" customWidth="1"/>
-    <col min="3" max="3" width="43.0390625" style="92" customWidth="1"/>
-    <col min="4" max="4" width="14.4296875" style="92" customWidth="1"/>
-    <col min="5" max="5" width="58.9609375" style="93" customWidth="1"/>
-    <col min="6" max="6" width="19.5234375" style="93" customWidth="1"/>
-    <col min="7" max="8" width="20.859375" style="93" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="93"/>
-    <col min="10" max="16384" width="9.140625" style="93"/>
+    <col min="1" max="1" width="19.859375" style="93"/>
+    <col min="2" max="2" width="18.859375" style="93" customWidth="1"/>
+    <col min="3" max="3" width="43.0390625" style="93" customWidth="1"/>
+    <col min="4" max="4" width="14.4296875" style="93" customWidth="1"/>
+    <col min="5" max="5" width="58.9609375" style="94" customWidth="1"/>
+    <col min="6" max="6" width="19.5234375" style="94" customWidth="1"/>
+    <col min="7" max="8" width="20.859375" style="94" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="94"/>
+    <col min="10" max="16384" width="9.140625" style="94"/>
   </cols>
   <sheetData>
-    <row r="1" s="91" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="94" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="95" t="s">
+    <row r="1" s="92" customFormat="1" ht="16" customHeight="1" spans="1:8">
+      <c r="A1" s="95" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="95" t="s">
+      <c r="C1" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="95" t="s">
+      <c r="D1" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="95" t="s">
+      <c r="E1" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="95" t="s">
+      <c r="F1" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="95" t="s">
+      <c r="G1" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="95" t="s">
+      <c r="H1" s="96" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="91" customFormat="1" ht="249.35" customHeight="1" spans="1:8">
-      <c r="A2" s="96"/>
-      <c r="B2" s="97"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="110">
+    <row r="2" s="92" customFormat="1" ht="249.35" customHeight="1" spans="1:8">
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="111">
         <f>D2*F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="109">
+      <c r="H2" s="110">
         <f>SUM(G2:G2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="91" customFormat="1" ht="251.35" customHeight="1" spans="1:8">
-      <c r="A3" s="96"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110">
+    <row r="3" s="92" customFormat="1" ht="251.35" customHeight="1" spans="1:8">
+      <c r="A3" s="97"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="109"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="111">
         <f>D3*F3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="111">
+      <c r="H3" s="112">
         <f>SUM(G3:G3)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" s="91" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A4" s="100"/>
-      <c r="B4" s="101"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="98"/>
-      <c r="E4" s="108"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110">
+    <row r="4" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A4" s="101"/>
+      <c r="B4" s="102"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111">
         <f>D4*F4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="111">
+      <c r="H4" s="112">
         <f>SUM(G4:G6)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" s="91" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A5" s="102"/>
-      <c r="B5" s="103"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="112"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="110">
+    <row r="5" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A5" s="103"/>
+      <c r="B5" s="104"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="113"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="111">
         <f>D5*F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="113"/>
-    </row>
-    <row r="6" s="91" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A6" s="105"/>
-      <c r="B6" s="106"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="110">
+      <c r="H5" s="114"/>
+    </row>
+    <row r="6" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="A6" s="106"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="115"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="111">
         <f>D6*F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="115"/>
-    </row>
-    <row r="7" s="91" customFormat="1" ht="200" customHeight="1" spans="1:8">
-      <c r="A7" s="96"/>
-      <c r="B7" s="97"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="116"/>
-      <c r="F7" s="111"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="109"/>
-    </row>
-    <row r="8" s="91" customFormat="1" spans="1:8">
-      <c r="A8" s="107"/>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117">
+      <c r="H6" s="116"/>
+    </row>
+    <row r="7" s="92" customFormat="1" ht="200" customHeight="1" spans="1:8">
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="110"/>
+    </row>
+    <row r="8" s="92" customFormat="1" spans="1:8">
+      <c r="A8" s="108"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="108"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118">
         <f>SUM(H2:H7)</f>
         <v>0</v>
       </c>
@@ -2039,199 +2038,199 @@
     <col min="4" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="5" width="34.5703125" customWidth="1"/>
     <col min="6" max="6" width="19.4296875" customWidth="1"/>
-    <col min="7" max="7" width="17.2890625" customWidth="1"/>
+    <col min="7" max="7" width="17.2890625" style="50" customWidth="1"/>
     <col min="9" max="9" width="13.0625"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:7">
-      <c r="A1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51" t="s">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="74" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A2" s="52"/>
+      <c r="A2" s="53"/>
       <c r="B2" s="39"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="75">
+      <c r="C2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="77">
         <f>SUM(D2*F2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="191" customHeight="1" spans="1:7">
-      <c r="A3" s="52"/>
+      <c r="A3" s="53"/>
       <c r="B3" s="39"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="75"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="77"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="52"/>
-      <c r="B4" s="57" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="57"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="78">
+      <c r="C4" s="58"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="80">
         <f>SUM(G2:G3)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="90"/>
+      <c r="I4" s="91"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="52"/>
-      <c r="B5" s="57" t="s">
+      <c r="A5" s="53"/>
+      <c r="B5" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="78">
+      <c r="C5" s="58"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="80">
         <f>G4*11%</f>
         <v>0</v>
       </c>
-      <c r="I5" s="90"/>
+      <c r="I5" s="91"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="52"/>
-      <c r="B6" s="57" t="s">
+      <c r="A6" s="53"/>
+      <c r="B6" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="78">
+      <c r="C6" s="58"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="80">
         <f>((G4*100)/111)*0.111%</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="52"/>
-      <c r="B7" s="57" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="81">
+      <c r="C7" s="58"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="80">
         <f>SUM(G4:G6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A8" s="52"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="61"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="75"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="77"/>
     </row>
     <row r="9" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A9" s="52"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="84"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="75"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="63"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="77"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="63"/>
-      <c r="B10" s="57" t="s">
+      <c r="A10" s="64"/>
+      <c r="B10" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="77"/>
-      <c r="G10" s="78">
+      <c r="C10" s="58"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="80">
         <f>SUM(G8:G9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="64"/>
-      <c r="B11" s="65" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="78">
+      <c r="C11" s="67"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="80">
         <f>G10*11%</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="63"/>
-      <c r="B12" s="57" t="s">
+      <c r="A12" s="64"/>
+      <c r="B12" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="57"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="78">
+      <c r="C12" s="58"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="80">
         <f>((G10*100)/111)*0.111%</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="67"/>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="68"/>
+      <c r="B13" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="69"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="79"/>
-      <c r="F13" s="86"/>
-      <c r="G13" s="81">
+      <c r="C13" s="70"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="80">
         <f>SUM(G10:G12)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="71"/>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="87">
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="88">
         <f>G7+G13</f>
         <v>0</v>
       </c>
-      <c r="F14" s="88"/>
-      <c r="G14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="21">

--- a/PROTOTYPE MONTHLY/FLOOR.xlsx
+++ b/PROTOTYPE MONTHLY/FLOOR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16020" windowHeight="17020" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="16140" windowHeight="17020" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Anugrah (Bag, Cup, Box)" sheetId="1" r:id="rId1"/>
@@ -61,6 +61,9 @@
     <t>GRAND TOTAL</t>
   </si>
   <si>
+    <t>SEE-U HTM DE / ECONO RED / 20 PK FSC MIX 85% / SUHT-046NN</t>
+  </si>
+  <si>
     <t>SALES PRICE</t>
   </si>
   <si>
@@ -70,13 +73,10 @@
     <t>PPh 22</t>
   </si>
   <si>
-    <t>STATUS</t>
+    <t>QTY</t>
   </si>
   <si>
     <t>DESCRIPTION</t>
-  </si>
-  <si>
-    <t>QTY</t>
   </si>
   <si>
     <t>NO</t>
@@ -107,17 +107,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="180" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="181" formatCode="[$-409]d\-mmm\-yyyy;@"/>
-    <numFmt numFmtId="182" formatCode="dd\-mmm"/>
-    <numFmt numFmtId="183" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="184" formatCode="[$Rp-421]#,##0.0000;[Red][$Rp-421]#,##0.0000"/>
-    <numFmt numFmtId="185" formatCode="[$Rp-421]#,##0.00;[Red][$Rp-421]#,##0.00"/>
+    <numFmt numFmtId="182" formatCode="[$Rp-421]#,##0.00;[Red][$Rp-421]#,##0.00"/>
+    <numFmt numFmtId="183" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="184" formatCode="dd\-mmm"/>
+    <numFmt numFmtId="185" formatCode="_ [$IDR]\ * #,##0_ ;_ [$IDR]\ * \-#,##0_ ;_ [$IDR]\ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="186" formatCode="[$Rp-421]#,##0.0000;[Red][$Rp-421]#,##0.0000"/>
   </numFmts>
   <fonts count="33">
     <font>
@@ -583,7 +584,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -631,7 +632,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -654,8 +657,32 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -673,43 +700,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -721,9 +711,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -864,7 +852,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -876,34 +864,34 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -988,7 +976,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1023,6 +1011,12 @@
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1041,49 +1035,61 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1092,44 +1098,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="183" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1141,16 +1147,16 @@
     <xf numFmtId="181" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1159,7 +1165,7 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1168,28 +1174,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1201,119 +1201,134 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="8" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="186" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="181" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1322,34 +1337,22 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1674,199 +1677,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="17.4296875" style="94"/>
-    <col min="2" max="2" width="13.4296875" style="94" customWidth="1"/>
-    <col min="3" max="3" width="36" style="94" customWidth="1"/>
-    <col min="4" max="4" width="21.2890625" style="93" customWidth="1"/>
-    <col min="5" max="5" width="33.2890625" style="94" customWidth="1"/>
-    <col min="6" max="6" width="17.2890625" style="94" customWidth="1"/>
-    <col min="7" max="8" width="20.859375" style="94" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="94"/>
-    <col min="10" max="10" width="12" style="94"/>
-    <col min="11" max="16384" width="18.0390625" style="94"/>
+    <col min="1" max="1" width="17.4296875" style="97"/>
+    <col min="2" max="2" width="13.4296875" style="97" customWidth="1"/>
+    <col min="3" max="3" width="36" style="97" customWidth="1"/>
+    <col min="4" max="4" width="21.2890625" style="95" customWidth="1"/>
+    <col min="5" max="5" width="33.2890625" style="97" customWidth="1"/>
+    <col min="6" max="6" width="17.2890625" style="97" customWidth="1"/>
+    <col min="7" max="8" width="20.859375" style="97" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="97"/>
+    <col min="10" max="10" width="15" style="97"/>
+    <col min="11" max="16384" width="18.0390625" style="97"/>
   </cols>
   <sheetData>
-    <row r="1" s="92" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="119" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="120" t="s">
+    <row r="1" s="93" customFormat="1" spans="1:8">
+      <c r="A1" s="128" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="C1" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="120" t="s">
+      <c r="D1" s="129" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="120" t="s">
+      <c r="E1" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="120" t="s">
+      <c r="F1" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="120" t="s">
+      <c r="G1" s="129" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="120" t="s">
+      <c r="H1" s="129" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="92" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A2" s="101"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="121"/>
-      <c r="D2" s="122"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="112">
-        <f t="shared" ref="G2:G10" si="0">SUM(D2*F2)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="112">
-        <f>SUM(G2:G5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="92" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A3" s="103"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="122"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="112">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H3" s="114"/>
-    </row>
-    <row r="4" s="92" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A4" s="103"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="122"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="112">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="114"/>
-    </row>
-    <row r="5" s="92" customFormat="1" ht="60" customHeight="1" spans="1:8">
-      <c r="A5" s="103"/>
-      <c r="B5" s="98"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="112">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="114"/>
-    </row>
-    <row r="6" s="92" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A6" s="101"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="112">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="112">
-        <f>SUM(G6:G9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="92" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A7" s="103"/>
-      <c r="B7" s="104"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="113"/>
-      <c r="F7" s="127"/>
-      <c r="G7" s="112">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="114"/>
-    </row>
-    <row r="8" s="92" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A8" s="103"/>
-      <c r="B8" s="104"/>
-      <c r="C8" s="98"/>
-      <c r="D8" s="98"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="112">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="114"/>
-    </row>
-    <row r="9" s="92" customFormat="1" ht="64.3" customHeight="1" spans="1:8">
-      <c r="A9" s="103"/>
-      <c r="B9" s="104"/>
-      <c r="C9" s="102"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="113"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="112">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="114"/>
-    </row>
-    <row r="10" s="92" customFormat="1" ht="258" customHeight="1" spans="1:8">
-      <c r="A10" s="97"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="128"/>
-      <c r="G10" s="110">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="110">
-        <f>SUM(G10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="92" customFormat="1" ht="18" customHeight="1" spans="1:8">
-      <c r="A11" s="123" t="s">
+    <row r="2" s="93" customFormat="1" spans="1:8">
+      <c r="A2" s="106"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133">
+        <f>SUM(D2*F2)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="133"/>
+    </row>
+    <row r="3" s="93" customFormat="1" spans="1:8">
+      <c r="A3" s="106"/>
+      <c r="B3" s="107"/>
+      <c r="C3" s="109"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="133"/>
+      <c r="G3" s="133">
+        <f>SUM(D3*F3)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="133"/>
+    </row>
+    <row r="4" s="93" customFormat="1" spans="1:8">
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="133"/>
+      <c r="G4" s="133">
+        <f>SUM(D4*F4)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="133"/>
+    </row>
+    <row r="5" s="93" customFormat="1" spans="1:8">
+      <c r="A5" s="106"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="133">
+        <f>SUM(D5*F5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="133"/>
+    </row>
+    <row r="6" s="93" customFormat="1" spans="1:8">
+      <c r="A6" s="106"/>
+      <c r="B6" s="107"/>
+      <c r="C6" s="107"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="134"/>
+      <c r="G6" s="133">
+        <f>SUM(D6*F6)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="133"/>
+    </row>
+    <row r="7" s="93" customFormat="1" spans="1:8">
+      <c r="A7" s="106"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="133">
+        <f>SUM(D7*F7)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="133"/>
+    </row>
+    <row r="8" s="93" customFormat="1" spans="1:8">
+      <c r="A8" s="106"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="107"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="133">
+        <f>SUM(D8*F8)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="133"/>
+    </row>
+    <row r="9" s="93" customFormat="1" spans="1:8">
+      <c r="A9" s="106"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="134"/>
+      <c r="G9" s="133">
+        <f>SUM(D9*F9)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="133"/>
+    </row>
+    <row r="10" s="93" customFormat="1" spans="1:8">
+      <c r="A10" s="106"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="107"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="134"/>
+      <c r="G10" s="133">
+        <f>SUM(D10*F10)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="133"/>
+    </row>
+    <row r="11" s="93" customFormat="1" spans="1:8">
+      <c r="A11" s="106"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="133">
+        <f>SUM(D11*F11)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="133"/>
+    </row>
+    <row r="12" s="93" customFormat="1" spans="1:8">
+      <c r="A12" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="124"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="126"/>
-      <c r="E11" s="129"/>
-      <c r="F11" s="129"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="131">
-        <f>SUM(H2:H10)</f>
+      <c r="B12" s="132"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="132"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="136">
+        <f>SUM(H2:H11)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="H6:H9"/>
+  <mergeCells count="1">
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1876,150 +1875,284 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="19.859375" style="93"/>
-    <col min="2" max="2" width="18.859375" style="93" customWidth="1"/>
-    <col min="3" max="3" width="43.0390625" style="93" customWidth="1"/>
-    <col min="4" max="4" width="14.4296875" style="93" customWidth="1"/>
-    <col min="5" max="5" width="58.9609375" style="94" customWidth="1"/>
-    <col min="6" max="6" width="19.5234375" style="94" customWidth="1"/>
-    <col min="7" max="8" width="20.859375" style="94" customWidth="1"/>
-    <col min="9" max="9" width="12.859375" style="94"/>
-    <col min="10" max="16384" width="9.140625" style="94"/>
+    <col min="1" max="1" width="19.859375" style="95"/>
+    <col min="2" max="2" width="21.6875" style="95" customWidth="1"/>
+    <col min="3" max="3" width="43.0390625" style="96" customWidth="1"/>
+    <col min="4" max="4" width="14.4296875" style="95" customWidth="1"/>
+    <col min="5" max="5" width="58.9609375" style="97" customWidth="1"/>
+    <col min="6" max="6" width="19.5234375" style="98" customWidth="1"/>
+    <col min="7" max="7" width="20.859375" style="98" customWidth="1"/>
+    <col min="8" max="8" width="20.859375" style="99" customWidth="1"/>
+    <col min="9" max="9" width="12.859375" style="97"/>
+    <col min="10" max="16384" width="9.140625" style="97"/>
   </cols>
   <sheetData>
-    <row r="1" s="92" customFormat="1" ht="16" customHeight="1" spans="1:8">
-      <c r="A1" s="95" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="96" t="s">
+    <row r="1" s="93" customFormat="1" spans="1:8">
+      <c r="A1" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="96" t="s">
+      <c r="C1" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="D1" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="E1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="96" t="s">
+      <c r="F1" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="96" t="s">
+      <c r="G1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="96" t="s">
+      <c r="H1" s="118" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="92" customFormat="1" ht="249.35" customHeight="1" spans="1:8">
-      <c r="A2" s="97"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="111">
+    <row r="2" s="93" customFormat="1" ht="23.2" spans="1:8">
+      <c r="A2" s="102"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="105"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119">
         <f>D2*F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="110">
-        <f>SUM(G2:G2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="92" customFormat="1" ht="251.35" customHeight="1" spans="1:8">
-      <c r="A3" s="97"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="109"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="111">
+      <c r="H2" s="119"/>
+    </row>
+    <row r="3" s="93" customFormat="1" ht="23.2" spans="1:8">
+      <c r="A3" s="102"/>
+      <c r="B3" s="103"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="105"/>
+      <c r="E3" s="103"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119">
         <f>D3*F3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="112">
-        <f>SUM(G3:G3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A4" s="101"/>
-      <c r="B4" s="102"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="111"/>
-      <c r="G4" s="111">
+      <c r="H3" s="119"/>
+    </row>
+    <row r="4" s="93" customFormat="1" spans="1:8">
+      <c r="A4" s="106"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="120"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121">
         <f>D4*F4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="112">
-        <f>SUM(G4:G6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
-      <c r="A5" s="103"/>
-      <c r="B5" s="104"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="112"/>
-      <c r="G5" s="111">
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" s="93" customFormat="1" spans="1:8">
+      <c r="A5" s="106"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121">
         <f>D5*F5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="114"/>
-    </row>
-    <row r="6" s="92" customFormat="1" ht="83" customHeight="1" spans="1:8">
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" s="94" customFormat="1" spans="1:8">
       <c r="A6" s="106"/>
       <c r="B6" s="107"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="111">
+      <c r="C6" s="109"/>
+      <c r="D6" s="108"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="121"/>
+      <c r="G6" s="121">
         <f>D6*F6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="116"/>
-    </row>
-    <row r="7" s="92" customFormat="1" ht="200" customHeight="1" spans="1:8">
-      <c r="A7" s="97"/>
-      <c r="B7" s="98"/>
-      <c r="C7" s="100"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="110"/>
-    </row>
-    <row r="8" s="92" customFormat="1" spans="1:8">
-      <c r="A8" s="108"/>
-      <c r="B8" s="108"/>
-      <c r="C8" s="108"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" s="94" customFormat="1" spans="1:8">
+      <c r="A7" s="106"/>
+      <c r="B7" s="107"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121">
+        <f t="shared" ref="G7:G14" si="0">F7*D7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" s="94" customFormat="1" spans="1:8">
+      <c r="A8" s="106"/>
+      <c r="B8" s="107"/>
+      <c r="C8" s="109"/>
       <c r="D8" s="108"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="108"/>
-      <c r="G8" s="118"/>
-      <c r="H8" s="118">
-        <f>SUM(H2:H7)</f>
+      <c r="E8" s="120"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" s="94" customFormat="1" spans="1:8">
+      <c r="A9" s="106"/>
+      <c r="B9" s="107"/>
+      <c r="C9" s="109"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" s="93" customFormat="1" spans="1:8">
+      <c r="A10" s="106"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="109"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" s="93" customFormat="1" spans="1:8">
+      <c r="A11" s="106"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="109"/>
+      <c r="D11" s="108"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" s="93" customFormat="1" spans="1:8">
+      <c r="A12" s="106"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="109"/>
+      <c r="D12" s="108"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="121"/>
+      <c r="G12" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" s="93" customFormat="1" spans="1:8">
+      <c r="A13" s="106"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="108"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" s="93" customFormat="1" spans="1:8">
+      <c r="A14" s="106"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="109"/>
+      <c r="D14" s="108"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="121">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" s="93" customFormat="1" spans="1:8">
+      <c r="A15" s="110"/>
+      <c r="B15" s="111"/>
+      <c r="C15" s="112"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="122"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="121">
+        <f>F15*D15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="123"/>
+    </row>
+    <row r="16" s="93" customFormat="1" spans="1:8">
+      <c r="A16" s="110"/>
+      <c r="B16" s="111"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="122"/>
+      <c r="F16" s="121"/>
+      <c r="G16" s="121">
+        <f>F16*D16</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="123"/>
+    </row>
+    <row r="17" s="93" customFormat="1" spans="1:8">
+      <c r="A17" s="110"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="113"/>
+      <c r="E17" s="122"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="121">
+        <f>F17*D17</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="123"/>
+    </row>
+    <row r="18" s="93" customFormat="1" spans="1:8">
+      <c r="A18" s="110"/>
+      <c r="B18" s="114"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="121">
+        <f>F18*D18</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="123"/>
+    </row>
+    <row r="19" s="93" customFormat="1" spans="1:8">
+      <c r="A19" s="115"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="115"/>
+      <c r="F19" s="126"/>
+      <c r="G19" s="127"/>
+      <c r="H19" s="127">
+        <f>SUM(H2:H18)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="H4:H6"/>
+  <mergeCells count="1">
+    <mergeCell ref="A19:E19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2029,232 +2162,225 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" customWidth="1"/>
     <col min="5" max="5" width="34.5703125" customWidth="1"/>
     <col min="6" max="6" width="19.4296875" customWidth="1"/>
-    <col min="7" max="7" width="17.2890625" style="50" customWidth="1"/>
+    <col min="7" max="7" width="17.2890625" style="56" customWidth="1"/>
     <col min="9" max="9" width="13.0625"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1" spans="1:7">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="52" t="s">
+      <c r="A1" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="74" t="s">
+      <c r="G1" s="76" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A2" s="53"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="77">
+      <c r="A2" s="59"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="61"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79">
         <f>SUM(D2*F2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" ht="191" customHeight="1" spans="1:7">
-      <c r="A3" s="53"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="77"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="79"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="53"/>
-      <c r="B4" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80">
+      <c r="A4" s="59"/>
+      <c r="B4" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="82">
         <f>SUM(G2:G3)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="91"/>
+      <c r="I4" s="92"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="53"/>
-      <c r="B5" s="58" t="s">
+      <c r="A5" s="59"/>
+      <c r="B5" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="82">
+        <f>G4*11%</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="92"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="59"/>
+      <c r="B6" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="64"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="82">
+        <f>((G4*100)/111)*0.111%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="59"/>
+      <c r="B7" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="64"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="82">
+        <f>SUM(G4:G6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="318.45" customHeight="1" spans="1:7">
+      <c r="A8" s="59"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="79">
+        <f>F8*D8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="59"/>
+      <c r="B9" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="80">
-        <f>G4*11%</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="91"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="53"/>
-      <c r="B6" s="58" t="s">
+      <c r="C9" s="64"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="82">
+        <f>SUM(G8:G8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="59"/>
+      <c r="B10" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="80">
-        <f>((G4*100)/111)*0.111%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="53"/>
-      <c r="B7" s="58" t="s">
+      <c r="C10" s="69"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="82">
+        <f>G9*11%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="59"/>
+      <c r="B11" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="64"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="82">
+        <f>((G9*100)/111)*0.111%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="59"/>
+      <c r="B12" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="80">
-        <f>SUM(G4:G6)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A8" s="53"/>
-      <c r="B8" s="60"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="77"/>
-    </row>
-    <row r="9" ht="123.5" customHeight="1" spans="1:7">
-      <c r="A9" s="53"/>
-      <c r="B9" s="63"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="84"/>
-      <c r="G9" s="77"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="64"/>
-      <c r="B10" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="79"/>
-      <c r="G10" s="80">
-        <f>SUM(G8:G9)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="65"/>
-      <c r="B11" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="79"/>
-      <c r="G11" s="80">
-        <f>G10*11%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="64"/>
-      <c r="B12" s="58" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="80">
-        <f>((G10*100)/111)*0.111%</f>
+      <c r="C12" s="72"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="82">
+        <f>SUM(G9:G11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="68"/>
-      <c r="B13" s="69" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="80">
-        <f>SUM(G10:G12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="71" t="s">
+      <c r="A13" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="72"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="88">
-        <f>G7+G13</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="89"/>
-      <c r="G14" s="90"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="89">
+        <f>SUM(G7,G12)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="90"/>
+      <c r="G13" s="91"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="18">
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:G13"/>
     <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A8:A12"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B8:B9"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E8:E9"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="G8:G9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2264,262 +2390,198 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="10.5703125" style="12" customWidth="1"/>
-    <col min="2" max="2" width="12.6015625" style="36" customWidth="1"/>
-    <col min="3" max="3" width="36.125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="18.828125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="12.2890625" style="12" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="12"/>
+    <col min="2" max="2" width="12.6015625" style="42" customWidth="1"/>
+    <col min="3" max="3" width="18.828125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.2890625" style="43" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" s="35" customFormat="1" ht="19" customHeight="1" spans="1:5">
-      <c r="A1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="38" t="s">
+    <row r="1" s="41" customFormat="1" ht="19" customHeight="1" spans="1:4">
+      <c r="A1" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="37" t="s">
+      <c r="C1" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="37" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" s="12" customFormat="1" ht="263.65" customHeight="1" spans="1:5">
-      <c r="A2" s="39"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="41"/>
-    </row>
-    <row r="3" s="12" customFormat="1" ht="255.1" customHeight="1" spans="1:5">
-      <c r="A3" s="39"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="48"/>
-    </row>
-    <row r="4" s="12" customFormat="1" ht="249.95" customHeight="1" spans="1:5">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="48"/>
-    </row>
-    <row r="5" s="12" customFormat="1" ht="256.25" customHeight="1" spans="1:5">
-      <c r="A5" s="39"/>
-      <c r="B5" s="40"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="48"/>
-    </row>
-    <row r="6" s="12" customFormat="1" ht="253.85" customHeight="1" spans="1:5">
-      <c r="A6" s="39"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" s="12" customFormat="1" ht="254.65" customHeight="1" spans="1:5">
-      <c r="A7" s="39"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="48"/>
-    </row>
-    <row r="8" s="12" customFormat="1" ht="255.35" customHeight="1" spans="1:5">
-      <c r="A8" s="39"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" s="12" customFormat="1" ht="266.95" customHeight="1" spans="1:5">
-      <c r="A9" s="39"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="48"/>
-    </row>
-    <row r="10" s="12" customFormat="1" ht="261.95" customHeight="1" spans="1:5">
-      <c r="A10" s="39"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="48"/>
-    </row>
-    <row r="11" s="12" customFormat="1" ht="261.9" customHeight="1" spans="1:5">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="48"/>
-    </row>
-    <row r="12" s="12" customFormat="1" ht="270.7" customHeight="1" spans="1:5">
-      <c r="A12" s="39"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="48"/>
-    </row>
-    <row r="13" s="12" customFormat="1" ht="261.1" customHeight="1" spans="1:5">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="48"/>
-    </row>
-    <row r="14" s="12" customFormat="1" ht="257.15" customHeight="1" spans="1:5">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="48"/>
-    </row>
-    <row r="15" s="12" customFormat="1" ht="263.55" customHeight="1" spans="1:5">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="48"/>
-    </row>
-    <row r="16" s="12" customFormat="1" ht="270.35" customHeight="1" spans="1:5">
-      <c r="A16" s="39"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="48"/>
-    </row>
-    <row r="17" s="12" customFormat="1" ht="261.7" customHeight="1" spans="1:5">
-      <c r="A17" s="39"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="48"/>
-    </row>
-    <row r="18" s="12" customFormat="1" ht="260" customHeight="1" spans="1:5">
-      <c r="A18" s="39"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="48"/>
-    </row>
-    <row r="19" s="12" customFormat="1" ht="263.2" customHeight="1" spans="1:5">
-      <c r="A19" s="39"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="48"/>
-    </row>
-    <row r="20" s="12" customFormat="1" ht="289.95" customHeight="1" spans="1:5">
-      <c r="A20" s="39"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="48"/>
-    </row>
-    <row r="21" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A21" s="39"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="48"/>
-    </row>
-    <row r="22" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A22" s="39"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="48"/>
-    </row>
-    <row r="23" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A23" s="39"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="48"/>
-    </row>
-    <row r="24" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A24" s="39"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="41"/>
-    </row>
-    <row r="25" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A25" s="39"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="41"/>
-    </row>
-    <row r="26" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A26" s="39"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="41"/>
-    </row>
-    <row r="27" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A27" s="39">
-        <v>45960</v>
-      </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="41"/>
-    </row>
-    <row r="28" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A28" s="39">
-        <v>45961</v>
-      </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="41"/>
-    </row>
-    <row r="29" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A29" s="39"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="41"/>
-    </row>
-    <row r="30" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A30" s="39"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="41"/>
-    </row>
-    <row r="31" s="12" customFormat="1" ht="200" customHeight="1" spans="1:5">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="41"/>
-    </row>
-    <row r="32" s="12" customFormat="1" spans="1:5">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="46">
-        <f>SUM(D2:D31)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="49"/>
+      <c r="D1" s="46" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" s="12" customFormat="1" ht="263.65" customHeight="1" spans="1:4">
+      <c r="A2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="50"/>
+    </row>
+    <row r="3" s="12" customFormat="1" ht="255.1" customHeight="1" spans="1:4">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+    </row>
+    <row r="4" s="12" customFormat="1" ht="249.95" customHeight="1" spans="1:4">
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+    </row>
+    <row r="5" s="12" customFormat="1" ht="256.25" customHeight="1" spans="1:4">
+      <c r="A5" s="47"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="50"/>
+    </row>
+    <row r="6" s="12" customFormat="1" ht="253.85" customHeight="1" spans="1:4">
+      <c r="A6" s="47"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="50"/>
+    </row>
+    <row r="7" s="12" customFormat="1" ht="255.35" customHeight="1" spans="1:4">
+      <c r="A7" s="47"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="50"/>
+    </row>
+    <row r="8" s="12" customFormat="1" ht="266.95" customHeight="1" spans="1:4">
+      <c r="A8" s="47"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="50"/>
+    </row>
+    <row r="9" s="12" customFormat="1" ht="261.95" customHeight="1" spans="1:4">
+      <c r="A9" s="47"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" s="12" customFormat="1" ht="261.9" customHeight="1" spans="1:4">
+      <c r="A10" s="47"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="50"/>
+    </row>
+    <row r="11" s="12" customFormat="1" ht="270.7" customHeight="1" spans="1:4">
+      <c r="A11" s="47"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="50"/>
+    </row>
+    <row r="12" s="12" customFormat="1" ht="261.1" customHeight="1" spans="1:4">
+      <c r="A12" s="47"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="50"/>
+    </row>
+    <row r="13" s="12" customFormat="1" ht="257.15" customHeight="1" spans="1:4">
+      <c r="A13" s="47"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="50"/>
+    </row>
+    <row r="14" s="12" customFormat="1" ht="263.55" customHeight="1" spans="1:4">
+      <c r="A14" s="47"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="50"/>
+    </row>
+    <row r="15" s="12" customFormat="1" ht="270.35" customHeight="1" spans="1:4">
+      <c r="A15" s="47"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="50"/>
+    </row>
+    <row r="16" s="12" customFormat="1" ht="261.7" customHeight="1" spans="1:4">
+      <c r="A16" s="47"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="50"/>
+    </row>
+    <row r="17" s="12" customFormat="1" ht="260" customHeight="1" spans="1:4">
+      <c r="A17" s="47"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="50"/>
+    </row>
+    <row r="18" s="12" customFormat="1" ht="289.95" customHeight="1" spans="1:4">
+      <c r="A18" s="47"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="50"/>
+    </row>
+    <row r="19" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="50"/>
+    </row>
+    <row r="20" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A20" s="47"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="50"/>
+    </row>
+    <row r="21" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A21" s="47"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="50"/>
+    </row>
+    <row r="22" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A22" s="47"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="50"/>
+    </row>
+    <row r="23" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A23" s="47"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="50"/>
+    </row>
+    <row r="24" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A24" s="47"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50"/>
+    </row>
+    <row r="25" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A25" s="47"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="50"/>
+    </row>
+    <row r="26" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A26" s="47"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="50"/>
+    </row>
+    <row r="27" s="12" customFormat="1" ht="200" customHeight="1" spans="1:4">
+      <c r="A27" s="47"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="50"/>
+    </row>
+    <row r="28" s="12" customFormat="1" spans="1:4">
+      <c r="A28" s="52"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="55">
+        <f>SUM(C:C)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:E32"/>
+  <mergeCells count="1">
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2534,105 +2596,113 @@
   <cols>
     <col min="1" max="1" width="21.140625" style="13" customWidth="1"/>
     <col min="2" max="2" width="27.5703125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="30.75" style="12" customWidth="1"/>
+    <col min="3" max="3" width="30.75" style="14" customWidth="1"/>
     <col min="4" max="4" width="65.703125" style="12" customWidth="1"/>
-    <col min="5" max="7" width="32.3359375" style="12" customWidth="1"/>
+    <col min="5" max="7" width="32.3359375" style="15" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" ht="35" customHeight="1" spans="1:7">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15" t="s">
+    <row r="1" s="11" customFormat="1" ht="28.8" spans="1:7">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="35" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" ht="240.3" customHeight="1" spans="1:7">
-      <c r="A2" s="16"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="26">
+    <row r="2" s="12" customFormat="1" ht="23.2" spans="1:7">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="37">
         <f>C2*E2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="27">
-        <f>SUM(F2:F2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="30"/>
-    </row>
-    <row r="4" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A4" s="20"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="31"/>
-    </row>
-    <row r="5" s="12" customFormat="1" ht="80" customHeight="1" spans="1:7">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="32"/>
+      <c r="G2" s="36"/>
+    </row>
+    <row r="3" s="12" customFormat="1" ht="26" spans="1:7">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="37">
+        <f>C3*E3</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="36"/>
+    </row>
+    <row r="4" s="12" customFormat="1" ht="26" spans="1:7">
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="37">
+        <f>C4*E4</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="36"/>
+    </row>
+    <row r="5" s="12" customFormat="1" ht="26" spans="1:7">
+      <c r="A5" s="29"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="37">
+        <f>C5*E5</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="39"/>
     </row>
     <row r="6" s="12" customFormat="1" ht="26" spans="1:7">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="33"/>
-    </row>
-    <row r="7" s="12" customFormat="1" ht="39" customHeight="1" spans="1:7">
-      <c r="A7" s="20" t="s">
+      <c r="A6" s="32"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="37">
+        <f>C6*E6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="39"/>
+    </row>
+    <row r="7" s="12" customFormat="1" ht="26" spans="1:7">
+      <c r="A7" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="34">
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="39">
         <f>SUM(G2:G6)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="G3:G5"/>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="D3:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2669,7 +2739,7 @@
         <v>18</v>
       </c>
       <c r="C2" s="8">
-        <f>'Anugrah (Bag, Cup, Box)'!H11</f>
+        <f>'Anugrah (Bag, Cup, Box)'!H12</f>
         <v>0</v>
       </c>
     </row>
@@ -2681,7 +2751,7 @@
         <v>19</v>
       </c>
       <c r="C3" s="8">
-        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H8</f>
+        <f>'UD Abdi Jaya (Bag, Cup, Box)'!H19</f>
         <v>0</v>
       </c>
     </row>
@@ -2693,7 +2763,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="8">
-        <f>'PT. SUPARMA JAYA TBK (Tissue)'!E14</f>
+        <f>'PT. SUPARMA JAYA TBK (Tissue)'!E13</f>
         <v>0</v>
       </c>
     </row>
@@ -2705,7 +2775,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="9">
-        <f>'Vickel Laundry'!C32</f>
+        <f>'Vickel Laundry'!D28</f>
         <v>0</v>
       </c>
     </row>
